--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_coquimbo.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_coquimbo.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.70479003292936</v>
+      </c>
+      <c r="C2">
         <v>29.11837593780765</v>
-      </c>
-      <c r="C2">
-        <v>27.70479003292936</v>
       </c>
       <c r="D2">
         <v>3.434257467297782</v>
       </c>
       <c r="E2">
+        <v>17.66626114288436</v>
+      </c>
+      <c r="F2">
+        <v>63.76608926429905</v>
+      </c>
+      <c r="G2">
         <v>18.5676495928166</v>
-      </c>
-      <c r="F2">
-        <v>63.76608926429903</v>
-      </c>
-      <c r="G2">
-        <v>17.66626114288436</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.76133925010603</v>
+      </c>
+      <c r="C3">
         <v>28.67334730231881</v>
-      </c>
-      <c r="C3">
-        <v>28.76133925010603</v>
       </c>
       <c r="D3">
         <v>3.487559333259742</v>
       </c>
       <c r="E3">
-        <v>18.21285253600753</v>
+        <v>18.26874361675607</v>
       </c>
       <c r="F3">
         <v>63.51840384723641</v>
       </c>
       <c r="G3">
-        <v>18.26874361675607</v>
+        <v>18.21285253600753</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>31.15303983228512</v>
+      </c>
+      <c r="C4">
         <v>36.74353598881901</v>
-      </c>
-      <c r="C4">
-        <v>31.15303983228512</v>
       </c>
       <c r="D4">
         <v>2.721567135793077</v>
       </c>
       <c r="E4">
-        <v>21.88462498959461</v>
+        <v>18.5548988595688</v>
       </c>
       <c r="F4">
         <v>59.56047615083659</v>
       </c>
       <c r="G4">
-        <v>18.5548988595688</v>
+        <v>21.88462498959461</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>34.37733035048471</v>
+      </c>
+      <c r="C5">
         <v>33.89261744966443</v>
-      </c>
-      <c r="C5">
-        <v>34.37733035048471</v>
       </c>
       <c r="D5">
         <v>2.95049504950495</v>
       </c>
       <c r="E5">
-        <v>20.14181254154664</v>
+        <v>20.42986926656326</v>
       </c>
       <c r="F5">
         <v>59.42831819189009</v>
       </c>
       <c r="G5">
-        <v>20.42986926656326</v>
+        <v>20.14181254154664</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.21419518377693</v>
+      </c>
+      <c r="C6">
         <v>35.5830164765526</v>
-      </c>
-      <c r="C6">
-        <v>29.21419518377693</v>
       </c>
       <c r="D6">
         <v>2.810329474621549</v>
       </c>
       <c r="E6">
+        <v>17.72736012305326</v>
+      </c>
+      <c r="F6">
+        <v>60.680638338781</v>
+      </c>
+      <c r="G6">
         <v>21.59200153816574</v>
-      </c>
-      <c r="F6">
-        <v>60.68063833878101</v>
-      </c>
-      <c r="G6">
-        <v>17.72736012305326</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.11120741021613</v>
+      </c>
+      <c r="C7">
         <v>33.1672173771735</v>
-      </c>
-      <c r="C7">
-        <v>27.11120741021613</v>
       </c>
       <c r="D7">
         <v>3.015025314388372</v>
       </c>
       <c r="E7">
-        <v>20.69350096319578</v>
+        <v>16.91506978944878</v>
       </c>
       <c r="F7">
         <v>62.39142924735543</v>
       </c>
       <c r="G7">
-        <v>16.91506978944878</v>
+        <v>20.69350096319578</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.13984233462273</v>
+      </c>
+      <c r="C8">
         <v>36.66944131616315</v>
-      </c>
-      <c r="C8">
-        <v>28.13984233462273</v>
       </c>
       <c r="D8">
         <v>2.727066364000534</v>
       </c>
       <c r="E8">
-        <v>22.24962120086753</v>
+        <v>17.07418521049348</v>
       </c>
       <c r="F8">
         <v>60.67619358863899</v>
       </c>
       <c r="G8">
-        <v>17.07418521049348</v>
+        <v>22.24962120086753</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>27.96927319283041</v>
+      </c>
+      <c r="C9">
         <v>49.65530825290526</v>
-      </c>
-      <c r="C9">
-        <v>27.96927319283041</v>
       </c>
       <c r="D9">
         <v>2.013883379611265</v>
       </c>
       <c r="E9">
-        <v>27.95520070969173</v>
+        <v>15.74628520736305</v>
       </c>
       <c r="F9">
         <v>56.29851408294522</v>
       </c>
       <c r="G9">
-        <v>15.74628520736306</v>
+        <v>27.95520070969173</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.73626677736267</v>
+      </c>
+      <c r="C10">
         <v>35.41580185415802</v>
-      </c>
-      <c r="C10">
-        <v>27.73626677736267</v>
       </c>
       <c r="D10">
         <v>2.823598359054503</v>
       </c>
       <c r="E10">
-        <v>21.70723433126961</v>
+        <v>17.00025443134594</v>
       </c>
       <c r="F10">
         <v>61.29251123738445</v>
       </c>
       <c r="G10">
-        <v>17.00025443134594</v>
+        <v>21.70723433126961</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>27.75696816128677</v>
+      </c>
+      <c r="C11">
         <v>33.19929492122948</v>
-      </c>
-      <c r="C11">
-        <v>27.75696816128677</v>
       </c>
       <c r="D11">
         <v>3.012112161937946</v>
       </c>
       <c r="E11">
-        <v>20.62628336755647</v>
+        <v>17.24503764544832</v>
       </c>
       <c r="F11">
-        <v>62.12867898699521</v>
+        <v>62.1286789869952</v>
       </c>
       <c r="G11">
-        <v>17.24503764544833</v>
+        <v>20.62628336755646</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>27.89221960255979</v>
+      </c>
+      <c r="C12">
         <v>31.20781407881442</v>
-      </c>
-      <c r="C12">
-        <v>27.89221960255979</v>
       </c>
       <c r="D12">
         <v>3.204325677775859</v>
       </c>
       <c r="E12">
+        <v>17.5312468245097</v>
+      </c>
+      <c r="F12">
+        <v>62.85353791958811</v>
+      </c>
+      <c r="G12">
         <v>19.61521525590218</v>
-      </c>
-      <c r="F12">
-        <v>62.85353791958812</v>
-      </c>
-      <c r="G12">
-        <v>17.53124682450971</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>25.19399249061327</v>
+      </c>
+      <c r="C13">
         <v>47.79724655819775</v>
-      </c>
-      <c r="C13">
-        <v>25.19399249061327</v>
       </c>
       <c r="D13">
         <v>2.092170725320765</v>
       </c>
       <c r="E13">
+        <v>14.56373896686442</v>
+      </c>
+      <c r="F13">
+        <v>57.80639560121545</v>
+      </c>
+      <c r="G13">
         <v>27.62986543192013</v>
-      </c>
-      <c r="F13">
-        <v>57.80639560121546</v>
-      </c>
-      <c r="G13">
-        <v>14.56373896686442</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>28.21269545407477</v>
+      </c>
+      <c r="C14">
         <v>34.05301853577716</v>
-      </c>
-      <c r="C14">
-        <v>28.21269545407477</v>
       </c>
       <c r="D14">
         <v>2.936597232780903</v>
       </c>
       <c r="E14">
-        <v>20.98596043395022</v>
+        <v>17.38672622846203</v>
       </c>
       <c r="F14">
         <v>61.62731333758775</v>
       </c>
       <c r="G14">
-        <v>17.38672622846203</v>
+        <v>20.98596043395022</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>28.62957937584803</v>
+      </c>
+      <c r="C15">
         <v>38.62957937584803</v>
-      </c>
-      <c r="C15">
-        <v>28.62957937584803</v>
       </c>
       <c r="D15">
         <v>2.588689848963821</v>
       </c>
       <c r="E15">
-        <v>23.09564370893161</v>
+        <v>17.11689786647197</v>
       </c>
       <c r="F15">
         <v>59.78745842459641</v>
       </c>
       <c r="G15">
-        <v>17.11689786647197</v>
+        <v>23.09564370893161</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>25.4871395167576</v>
+      </c>
+      <c r="C16">
         <v>50.4676539360873</v>
-      </c>
-      <c r="C16">
-        <v>25.4871395167576</v>
       </c>
       <c r="D16">
         <v>1.981467181467181</v>
       </c>
       <c r="E16">
-        <v>28.68217054263566</v>
+        <v>14.48504983388705</v>
       </c>
       <c r="F16">
         <v>56.8327796234773</v>
       </c>
       <c r="G16">
-        <v>14.48504983388705</v>
+        <v>28.68217054263566</v>
       </c>
     </row>
   </sheetData>
